--- a/source/data/прайс-для-яндекса.xlsx
+++ b/source/data/прайс-для-яндекса.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L70"/>
+  <dimension ref="A1:L136"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u08-podveska.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u08-podveska.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3671,6 +3671,3042 @@
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Ремонт глушителя Красногорск</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Ремонт глушителя</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>70</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Устраняем прогар и посторонний гул, варим аргоном, при необходимости меняем банку. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Устраняем прогар и посторонний гул, варим аргоном, при необходимости меняем банку</t>
+        </is>
+      </c>
+      <c r="F71" t="n">
+        <v>1</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Ремонт глушителя Красногорск</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Замена глушителя в сборе</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>71</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Подбор и установка нового глушителя под вашу модель. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Подбор и установка нового глушителя под вашу модель</t>
+        </is>
+      </c>
+      <c r="F72" t="n">
+        <v>1</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Замена гофры глушителя</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Замена гофры</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>72</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>Вырезаем прогоревшую гофру, ставим новую с проваром по кругу. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>Вырезаем прогоревшую гофру, ставим новую с проваром по кругу</t>
+        </is>
+      </c>
+      <c r="F73" t="n">
+        <v>1</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Замена резонатора</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Замена резонатора</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>73</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>Замена среднего элемента выхлопа, подгонка по месту. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Замена среднего элемента выхлопа, подгонка по месту</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>1</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Пламегаситель</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Установка пламегасителя</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>74</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Пламегаситель вместо изношенного катализатора: без ошибок и без потери тяги. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Пламегаситель вместо изношенного катализатора: без ошибок и без потери тяги</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>1</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Пламегаситель</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Замена пламегасителя</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>75</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>Меняем прогоревший пламегаситель, восстанавливаем герметичность тракта. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Меняем прогоревший пламегаситель, восстанавливаем герметичность тракта</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>1</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Стронгер</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Установка стронгера</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>76</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Спортивный катколлектор-стронгер: звук тише, чем на прямотоке, ошибок нет. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Спортивный катколлектор-стронгер: звук тише, чем на прямотоке, ошибок нет</t>
+        </is>
+      </c>
+      <c r="F77" t="n">
+        <v>1</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Прямоток</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Установка прямоточной выхлопной системы</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>77</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Подбираем звук под пожелания и варим по месту, без дребезга и прогаров. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Подбираем звук под пожелания и варим по месту, без дребезга и прогаров</t>
+        </is>
+      </c>
+      <c r="F78" t="n">
+        <v>1</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Замена катализатора</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Замена катализатора</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>78</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Замена на новый катализатор или на пламегаситель — на выбор, с прошивкой. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Замена на новый катализатор или на пламегаситель — на выбор, с прошивкой</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>1</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u03-katalizator.png</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Удаление катализатора Красногорск</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Удаление катализатора с прошивкой</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>79</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Механическое удаление и корректная программная настройка, чтобы не горел Check. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Механическое удаление и корректная программная настройка, чтобы не горел Check</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>1</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u03-katalizator.png</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Замер противодавления</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Замер противодавления выхлопа</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>80</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Точная проверка, забит катализатор или нет, до того как что-то резать. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Точная проверка, забит катализатор или нет, до того как что-то резать</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>1</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Замена лямбда-зонда</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Замена датчика кислорода (лямбда-зонда)</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>81</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Подбор и замена лямбда-зонда, проверка показаний по сканеру. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Подбор и замена лямбда-зонда, проверка показаний по сканеру</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>1</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Обманка лямбда-зонда</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Установка обманки лямбда-зонда</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>82</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Механическая или программная обманка после удаления катализатора. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Механическая или программная обманка после удаления катализатора</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>1</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Прогар выпускного коллектора</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Ремонт прогара выпускного коллектора</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>83</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>Снятие, проверка плоскости, замена прокладок и шпилек. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Снятие, проверка плоскости, замена прокладок и шпилек</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>1</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Сварка выхлопной системы</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Сварка выхлопа аргоном</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>84</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Аргонная сварка нержавейки — шов держится, а не рассыпается через сезон. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Аргонная сварка нержавейки — шов держится, а не рассыпается через сезон</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Крепления глушителя</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Замена подвесов и хомутов глушителя</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>85</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Меняем порванные резинки и хомуты — уходит стук и провисание трубы. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Меняем порванные резинки и хомуты — уходит стук и провисание трубы</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="L86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Теплозащита выхлопа</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Ремонт и замена теплозащитных экранов</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>86</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Убираем дребезг от прогоревших экранов над выхлопом. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Убираем дребезг от прогоревших экранов над выхлопом</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>1</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Диагностика выхлопа Москва</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Осмотр выхлопной системы на подъёмнике</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>87</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Ищем прогары, подсосы и трещины, показываем всё на машине. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Ищем прогары, подсосы и трещины, показываем всё на машине</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>1</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Промывка сажевого фильтра</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Промывка сажевого фильтра DPF</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>88</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Химическая промывка без снятия или со снятием — по состоянию фильтра. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Химическая промывка без снятия или со снятием — по состоянию фильтра</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>1</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u04-dpf.png</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Удаление сажевого фильтра</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Удаление DPF с прошивкой</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>89</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Механическое удаление и настройка блока управления под работу без сажевого. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Механическое удаление и настройка блока управления под работу без сажевого</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>1</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u04-dpf.png</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Удаление AdBlue</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Отключение системы AdBlue</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>90</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Программное отключение мочевины, снятие ограничений по мощности и запуску. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Программное отключение мочевины, снятие ограничений по мощности и запуску</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>1</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u04-dpf.png</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Отключение SCR</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Отключение системы SCR</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>91</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Настройка блока после отказа катализатора SCR на дизеле. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Настройка блока после отказа катализатора SCR на дизеле</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>1</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u04-dpf.png</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Дизельный сервис Красногорск</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Диагностика дизельного двигателя</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>92</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Проверка топливной аппаратуры, обратки, давления и сажевого фильтра. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Проверка топливной аппаратуры, обратки, давления и сажевого фильтра</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>1</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u12-dvigatel.png</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="L93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Дизельный сервис Красногорск</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Замена свечей накаливания</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>93</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Замена свечей накала, проверка реле и проводки — уходит тяжёлый холодный пуск. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Замена свечей накала, проверка реле и проводки — уходит тяжёлый холодный пуск</t>
+        </is>
+      </c>
+      <c r="F94" t="n">
+        <v>1</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u12-dvigatel.png</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr"/>
+      <c r="L94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Чип-тюнинг Красногорск</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Чип-тюнинг с диагностикой</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>94</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Диагностика, снятие заводской прошивки, настройка и проверка на выходе. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Диагностика, снятие заводской прошивки, настройка и проверка на выходе</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>1</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u05-chip-tyuning.png</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="L95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Чип-тюнинг Stage 2</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>95</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Настройка под доработанный выпуск и впуск. Делаем после замера на месте. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Настройка под доработанный выпуск и впуск</t>
+        </is>
+      </c>
+      <c r="F96" t="n">
+        <v>1</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u05-chip-tyuning.png</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="L96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Отключение ошибок двигателя</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Устранение ошибки Check Engine</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>96</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Находим настоящую причину, а не гасим лампу. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Находим настоящую причину, а не гасим лампу</t>
+        </is>
+      </c>
+      <c r="F97" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Автосервис Опалиха</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Компьютерная диагностика автомобиля</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>97</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Полная диагностика по всем блокам, разбор причины простыми словами. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Полная диагностика по всем блокам, разбор причины простыми словами</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>1</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Автосервис Опалиха</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Ремонт выхлопной системы</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>98</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Сварка, замена гофры, резонатора и банки глушителя. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Сварка, замена гофры, резонатора и банки глушителя</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>1</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="L99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Автосервис Нахабино</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Замена масла и фильтров</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>99</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Плановое обслуживание: масло, фильтры, осмотр по регламенту. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Плановое обслуживание: масло, фильтры, осмотр по регламенту</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u07-maslo.png</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="L100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Автосервис Нахабино</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Удаление катализатора</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>100</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Удаление с установкой пламегасителя и корректной прошивкой. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Удаление с установкой пламегасителя и корректной прошивкой</t>
+        </is>
+      </c>
+      <c r="F101" t="n">
+        <v>1</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u03-katalizator.png</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="L101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Автосервис Митино</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Ремонт глушителя</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>101</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Устранение прогара и гула, аргонная сварка. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>Устранение прогара и гула, аргонная сварка</t>
+        </is>
+      </c>
+      <c r="F102" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Автосервис Митино</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Диагностика подвески</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>102</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Осмотр на подъёмнике, показываем каждый люфт руками. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>Осмотр на подъёмнике, показываем каждый люфт руками</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>1</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Автосервис Строгино</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Чип-тюнинг</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>103</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Настройка блока управления двигателем с обязательной диагностикой до работ. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>Настройка блока управления двигателем с обязательной диагностикой до работ</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>1</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u05-chip-tyuning.png</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Автосервис Волоколамское шоссе</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Ремонт ходовой части</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>104</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Рычаги, стойки, сайлентблоки, шаровые — со сметой до начала работ. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>Рычаги, стойки, сайлентблоки, шаровые — со сметой до начала работ</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>1</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr"/>
+      <c r="K105" t="inlineStr"/>
+      <c r="L105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>СТО рядом со мной</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Плановое техническое обслуживание</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>105</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Масло, фильтры, осмотр по 30 пунктам, отметка в сервисной книжке. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>Масло, фильтры, осмотр по 30 пунктам, отметка в сервисной книжке</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>1</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr"/>
+      <c r="K106" t="inlineStr"/>
+      <c r="L106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Автосервис недорого Красногорск</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Дефектовка перед ремонтом</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>106</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Разбираем узел, показываем износ и называем итоговую сумму до начала работ. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>Разбираем узел, показываем износ и называем итоговую сумму до начала работ</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>1</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr"/>
+      <c r="K107" t="inlineStr"/>
+      <c r="L107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Замена тормозных дисков</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Замена тормозных дисков</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>107</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>Замена дисков в паре, обслуживание суппортов и направляющих. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>Замена дисков в паре, обслуживание суппортов и направляющих</t>
+        </is>
+      </c>
+      <c r="F108" t="n">
+        <v>1</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u09-tormoza.png</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr"/>
+      <c r="L108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Замена тормозной жидкости</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Замена тормозной жидкости с прокачкой</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>108</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>Полная замена по всем контурам, проверка педали. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>Полная замена по всем контурам, проверка педали</t>
+        </is>
+      </c>
+      <c r="F109" t="n">
+        <v>1</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u09-tormoza.png</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="L109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Ремонт суппортов</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Обслуживание тормозных суппортов</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>109</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Чистка, смазка направляющих, замена пыльников и поршней. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Чистка, смазка направляющих, замена пыльников и поршней</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>1</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u09-tormoza.png</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr"/>
+      <c r="K110" t="inlineStr"/>
+      <c r="L110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Замена амортизаторов</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Замена амортизаторов</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>110</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Замена стоек в паре, осмотр опор и пружин, развал-схождение после. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>Замена стоек в паре, осмотр опор и пружин, развал-схождение после</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>1</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr"/>
+      <c r="K111" t="inlineStr"/>
+      <c r="L111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Замена пружин подвески</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Замена пружин</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>111</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>Замена просевших или лопнувших пружин, проверка отбойников. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>Замена просевших или лопнувших пружин, проверка отбойников</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>1</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr"/>
+      <c r="K112" t="inlineStr"/>
+      <c r="L112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Замена шаровых опор</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Замена шаровой опоры</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>112</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>Замена шаровых, проверка пыльников и рычагов. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>Замена шаровых, проверка пыльников и рычагов</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>1</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u08-podveska.png</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
+      <c r="L113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Замена рулевых наконечников</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Замена рулевых наконечников и тяг</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>113</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>Устраняем люфт руля, после работ делаем развал-схождение. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>Устраняем люфт руля, после работ делаем развал-схождение</t>
+        </is>
+      </c>
+      <c r="F114" t="n">
+        <v>1</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Замена ШРУСа</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Замена ШРУСа и пыльника</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>114</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>Хруст при повороте — меняем шарнир или пыльник, пока не рассыпалось. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Хруст при повороте — меняем шарнир или пыльник, пока не рассыпалось</t>
+        </is>
+      </c>
+      <c r="F115" t="n">
+        <v>1</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Замена рычагов подвески</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Замена рычагов</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>115</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Замена рычагов в сборе или перепрессовка сайлентблоков. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Замена рычагов в сборе или перепрессовка сайлентблоков</t>
+        </is>
+      </c>
+      <c r="F116" t="n">
+        <v>1</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u08-podveska.png</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Замена ступичного подшипника</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Замена ступичного подшипника</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>116</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Уходит гул на скорости. Меняем подшипник или ступицу в сборе. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Уходит гул на скорости</t>
+        </is>
+      </c>
+      <c r="F117" t="n">
+        <v>1</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr"/>
+      <c r="L117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Замена цепи ГРМ</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Замена цепи ГРМ</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>117</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Замена цепи с натяжителем и успокоителями по регламенту. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Замена цепи с натяжителем и успокоителями по регламенту</t>
+        </is>
+      </c>
+      <c r="F118" t="n">
+        <v>1</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u06-grm.png</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr"/>
+      <c r="K118" t="inlineStr"/>
+      <c r="L118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Замена сальников двигателя</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Замена сальника коленвала</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>118</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Устраняем течь масла, проверяем сапун и давление картерных газов. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Устраняем течь масла, проверяем сапун и давление картерных газов</t>
+        </is>
+      </c>
+      <c r="F119" t="n">
+        <v>1</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr"/>
+      <c r="K119" t="inlineStr"/>
+      <c r="L119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Замена сцепления</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Замена комплекта сцепления</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>119</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Замена диска, корзины и выжимного, осмотр маховика. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Замена диска, корзины и выжимного, осмотр маховика</t>
+        </is>
+      </c>
+      <c r="F120" t="n">
+        <v>1</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Замена масла в МКПП</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Замена масла в механической коробке</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>120</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Замена трансмиссионного масла, осмотр сальников. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Замена трансмиссионного масла, осмотр сальников</t>
+        </is>
+      </c>
+      <c r="F121" t="n">
+        <v>1</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u07-maslo.png</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Замена масла в АКПП</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Замена масла в автоматической коробке</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>121</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Частичная или полная замена с фильтром и очисткой поддона. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>Частичная или полная замена с фильтром и очисткой поддона</t>
+        </is>
+      </c>
+      <c r="F122" t="n">
+        <v>1</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u07-maslo.png</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr"/>
+      <c r="K122" t="inlineStr"/>
+      <c r="L122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Замена радиатора</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Замена радиатора охлаждения</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>122</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Замена радиатора и патрубков, заливка антифриза, проверка на утечки. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>Замена радиатора и патрубков, заливка антифриза, проверка на утечки</t>
+        </is>
+      </c>
+      <c r="F123" t="n">
+        <v>1</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Промывка системы охлаждения</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Промывка системы охлаждения</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>123</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>Удаляем отложения, из-за которых машина греется в пробках. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Удаляем отложения, из-за которых машина греется в пробках</t>
+        </is>
+      </c>
+      <c r="F124" t="n">
+        <v>1</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Замена ремня генератора</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Замена ремня навесного оборудования</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>124</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Замена ремня, роликов и натяжителя — уходит свист при пуске. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Замена ремня, роликов и натяжителя — уходит свист при пуске</t>
+        </is>
+      </c>
+      <c r="F125" t="n">
+        <v>1</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u12-dvigatel.png</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr"/>
+      <c r="K125" t="inlineStr"/>
+      <c r="L125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Замена аккумулятора</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Подбор и замена аккумулятора</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>125</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Проверка АКБ под нагрузкой, подбор по машине, регистрация при необходимости. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Проверка АКБ под нагрузкой, подбор по машине, регистрация при необходимости</t>
+        </is>
+      </c>
+      <c r="F126" t="n">
+        <v>1</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr"/>
+      <c r="K126" t="inlineStr"/>
+      <c r="L126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Проверка генератора</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Диагностика зарядки и генератора</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>126</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>Замер тока зарядки, проверка щёток, реле-регулятора и ремня. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Замер тока зарядки, проверка щёток, реле-регулятора и ремня</t>
+        </is>
+      </c>
+      <c r="F127" t="n">
+        <v>1</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u11-starter.png</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Поиск утечки тока</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Поиск утечки тока</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>127</v>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>Ищем, что разряжает аккумулятор за ночь. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Ищем, что разряжает аккумулятор за ночь</t>
+        </is>
+      </c>
+      <c r="F128" t="n">
+        <v>1</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Замена датчиков двигателя</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Замена датчика коленвала и распредвала</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>128</v>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>Подбор и замена датчиков, проверка сигнала по сканеру. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Подбор и замена датчиков, проверка сигнала по сканеру</t>
+        </is>
+      </c>
+      <c r="F129" t="n">
+        <v>1</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Диагностика ABS</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Диагностика и ремонт ABS</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>129</v>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>Проверка датчиков и блока, устранение горящей лампы ABS. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>Проверка датчиков и блока, устранение горящей лампы ABS</t>
+        </is>
+      </c>
+      <c r="F130" t="n">
+        <v>1</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Регулировка фар</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Регулировка света фар</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>130</v>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Настройка на стенде, чтобы не слепить встречных и видеть дорогу. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>Настройка на стенде, чтобы не слепить встречных и видеть дорогу</t>
+        </is>
+      </c>
+      <c r="F131" t="n">
+        <v>1</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr"/>
+      <c r="K131" t="inlineStr"/>
+      <c r="L131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Замена ламп</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Замена ламп головного света</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>131</v>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Подбор и установка ламп, проверка проводки и разъёмов. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>Подбор и установка ламп, проверка проводки и разъёмов</t>
+        </is>
+      </c>
+      <c r="F132" t="n">
+        <v>1</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr"/>
+      <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Замена салонного фильтра</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Замена салонного фильтра</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>132</v>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Замена фильтра и обработка испарителя — уходит запах из печки. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>Замена фильтра и обработка испарителя — уходит запах из печки</t>
+        </is>
+      </c>
+      <c r="F133" t="n">
+        <v>1</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr"/>
+      <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Замена воздушного фильтра</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Замена воздушного фильтра</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>133</v>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>Замена фильтра, осмотр патрубков впуска на подсос. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>Замена фильтра, осмотр патрубков впуска на подсос</t>
+        </is>
+      </c>
+      <c r="F134" t="n">
+        <v>1</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr"/>
+      <c r="K134" t="inlineStr"/>
+      <c r="L134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Сезонное обслуживание</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Подготовка автомобиля к зиме</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>134</v>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>Аккумулятор, свечи, антифриз, щётки, печка — одним заездом. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Аккумулятор, свечи, антифриз, щётки, печка — одним заездом</t>
+        </is>
+      </c>
+      <c r="F135" t="n">
+        <v>1</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Сезонное обслуживание</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Подготовка автомобиля к лету</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>135</v>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>Кондиционер, охлаждение, тормоза, салонный фильтр. Актуальную стоимость уточните по телефону.</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Кондиционер, охлаждение, тормоза, салонный фильтр</t>
+        </is>
+      </c>
+      <c r="F136" t="n">
+        <v>1</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>Нет</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>Да</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/source/data/прайс-для-яндекса.xlsx
+++ b/source/data/прайс-для-яндекса.xlsx
@@ -527,7 +527,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u07-maslo.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u07-maslo.png</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u12-dvigatel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u12-dvigatel.png</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u07-maslo.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u07-maslo.png</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -711,7 +711,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u07-maslo.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u07-maslo.png</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -757,7 +757,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u12-dvigatel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u12-dvigatel.png</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u12-dvigatel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u12-dvigatel.png</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u12-dvigatel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u12-dvigatel.png</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u07-maslo.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u07-maslo.png</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u08-podveska.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u08-podveska.png</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1033,7 +1033,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u12-dvigatel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u12-dvigatel.png</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1079,7 +1079,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u07-maslo.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u07-maslo.png</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1125,7 +1125,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u12-dvigatel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u12-dvigatel.png</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u12-dvigatel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u12-dvigatel.png</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1309,7 +1309,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u08-podveska.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u08-podveska.png</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u08-podveska.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u08-podveska.png</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u08-podveska.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u08-podveska.png</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u08-podveska.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u08-podveska.png</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1539,7 +1539,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u12-dvigatel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u12-dvigatel.png</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1585,7 +1585,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u12-dvigatel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u12-dvigatel.png</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u06-grm.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u06-grm.png</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u07-maslo.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u07-maslo.png</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -1815,7 +1815,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u12-dvigatel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u12-dvigatel.png</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u12-dvigatel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u12-dvigatel.png</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u13-endoskopiya.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u13-endoskopiya.png</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u12-dvigatel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u12-dvigatel.png</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -1999,7 +1999,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -2045,7 +2045,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u03-katalizator.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u03-katalizator.png</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -2137,7 +2137,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u04-dpf.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u04-dpf.png</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -2183,7 +2183,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u05-chip-tyuning.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u05-chip-tyuning.png</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u05-chip-tyuning.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u05-chip-tyuning.png</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u05-chip-tyuning.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u05-chip-tyuning.png</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u05-chip-tyuning.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u05-chip-tyuning.png</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u05-chip-tyuning.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u05-chip-tyuning.png</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u05-chip-tyuning.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u05-chip-tyuning.png</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -2459,7 +2459,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u05-chip-tyuning.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u05-chip-tyuning.png</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u05-chip-tyuning.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u05-chip-tyuning.png</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u18-klyuchi.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u18-klyuchi.png</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -2597,7 +2597,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u05-chip-tyuning.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u05-chip-tyuning.png</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u11-starter.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u11-starter.png</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2781,7 +2781,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2827,7 +2827,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u07-maslo.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u07-maslo.png</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -2873,7 +2873,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u14-predprodazhnaya.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u14-predprodazhnaya.png</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u13-endoskopiya.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u13-endoskopiya.png</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -3011,7 +3011,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u06-grm.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u06-grm.png</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -3057,7 +3057,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u07-maslo.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u07-maslo.png</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u12-dvigatel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u12-dvigatel.png</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u07-maslo.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u07-maslo.png</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u15-pechka.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u15-pechka.png</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u10-konditsioner.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u10-konditsioner.png</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -3287,7 +3287,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u09-tormoza.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u09-tormoza.png</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -3379,7 +3379,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u16-shinomontazh.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u16-shinomontazh.png</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
@@ -3425,7 +3425,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u11-starter.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u11-starter.png</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u18-klyuchi.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u18-klyuchi.png</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -3517,7 +3517,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u18-klyuchi.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u18-klyuchi.png</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u18-klyuchi.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u18-klyuchi.png</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -3609,7 +3609,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u18-klyuchi.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u18-klyuchi.png</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -3655,7 +3655,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u17-dopoborudovanie.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u17-dopoborudovanie.png</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -3839,7 +3839,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3931,7 +3931,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3977,7 +3977,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -4023,7 +4023,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u03-katalizator.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u03-katalizator.png</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -4115,7 +4115,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u03-katalizator.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u03-katalizator.png</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4207,7 +4207,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -4253,7 +4253,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -4345,7 +4345,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4391,7 +4391,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -4437,7 +4437,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4483,7 +4483,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -4529,7 +4529,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u04-dpf.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u04-dpf.png</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u04-dpf.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u04-dpf.png</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u04-dpf.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u04-dpf.png</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u04-dpf.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u04-dpf.png</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -4713,7 +4713,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u12-dvigatel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u12-dvigatel.png</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u12-dvigatel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u12-dvigatel.png</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u05-chip-tyuning.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u05-chip-tyuning.png</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u05-chip-tyuning.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u05-chip-tyuning.png</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4943,7 +4943,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4989,7 +4989,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -5035,7 +5035,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u07-maslo.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u07-maslo.png</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u03-katalizator.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u03-katalizator.png</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -5127,7 +5127,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -5173,7 +5173,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u02-glushitel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u02-glushitel.png</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -5219,7 +5219,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u05-chip-tyuning.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u05-chip-tyuning.png</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -5311,7 +5311,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
@@ -5357,7 +5357,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u09-tormoza.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u09-tormoza.png</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
@@ -5449,7 +5449,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u09-tormoza.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u09-tormoza.png</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -5495,7 +5495,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u09-tormoza.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u09-tormoza.png</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
@@ -5541,7 +5541,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
@@ -5587,7 +5587,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -5633,7 +5633,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u08-podveska.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u08-podveska.png</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
@@ -5679,7 +5679,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
@@ -5725,7 +5725,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u08-podveska.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u08-podveska.png</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -5863,7 +5863,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u06-grm.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u06-grm.png</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -5909,7 +5909,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u07-maslo.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u07-maslo.png</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u07-maslo.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u07-maslo.png</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
@@ -6093,7 +6093,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -6185,7 +6185,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u12-dvigatel.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u12-dvigatel.png</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
@@ -6277,7 +6277,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u11-starter.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u11-starter.png</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
@@ -6369,7 +6369,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -6415,7 +6415,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -6461,7 +6461,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
@@ -6553,7 +6553,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
@@ -6599,7 +6599,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
@@ -6645,7 +6645,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/u01-diagnostika.png</t>
+          <t>https://raw.githubusercontent.com/sabushmustafaev1990-ai/vyhlop-expert-cards/main/v2/u01-diagnostika.png</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
